--- a/00-inbox/IBC-DETAILS.xlsx
+++ b/00-inbox/IBC-DETAILS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="GRANULES TO IC" sheetId="10" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="152">
   <si>
     <t>G P COIL - 1.20 X 88 MM</t>
   </si>
@@ -447,16 +447,10 @@
     <t>BTF 3 INCH</t>
   </si>
   <si>
-    <t>DN80</t>
-  </si>
-  <si>
     <t>DG CAP</t>
   </si>
   <si>
     <t>D15</t>
-  </si>
-  <si>
-    <t>1000 LTR IBC HM-HDPE BULK CONTAINER CP-FLAT DN75 QD BV 2.5 INCH</t>
   </si>
   <si>
     <t>Item Details</t>
@@ -473,6 +467,18 @@
   </si>
   <si>
     <t>( NOS)</t>
+  </si>
+  <si>
+    <t>CAGE TYPE</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>DN50</t>
+  </si>
+  <si>
+    <t>1000 LTR IBC HM-HDPE BULK CONTAINER CP-FLAT DN50 QD BV 2.5 INCH</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1356,7 @@
       <c r="C4" s="31"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
@@ -3371,7 +3377,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="28.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="21" bestFit="1" customWidth="1"/>
@@ -3390,19 +3396,19 @@
     </row>
     <row r="2" spans="1:6" s="22" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="46" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E2" s="47"/>
     </row>
     <row r="3" spans="1:6" s="48" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F3" s="49"/>
     </row>
@@ -3450,7 +3456,7 @@
         <v>114</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E6" s="53">
         <v>1</v>
@@ -3486,7 +3492,7 @@
         <v>117</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E8" s="53">
         <v>1</v>
@@ -3522,7 +3528,7 @@
         <v>120</v>
       </c>
       <c r="D10" s="54" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E10" s="53">
         <v>1</v>
@@ -3548,17 +3554,13 @@
       <c r="F11" s="58"/>
     </row>
     <row r="12" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>21</v>
-      </c>
+      <c r="A12" s="50"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="51" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="E12" s="53">
         <v>1</v>
@@ -3570,66 +3572,68 @@
         <v>109</v>
       </c>
       <c r="B13" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="53">
+        <v>1</v>
+      </c>
+      <c r="F13" s="58"/>
+    </row>
+    <row r="14" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C14" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="53">
-        <v>1</v>
-      </c>
-      <c r="F13" s="58"/>
-    </row>
-    <row r="14" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="51" t="s">
+      <c r="D14" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="53">
+        <v>1</v>
+      </c>
+      <c r="F14" s="58"/>
+    </row>
+    <row r="15" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D15" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E15" s="53">
         <v>4</v>
       </c>
-      <c r="F14" s="58"/>
-    </row>
-    <row r="15" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="D15" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" s="53">
-        <v>1</v>
-      </c>
       <c r="F15" s="58"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
         <v>109</v>
       </c>
       <c r="B16" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="26">
-        <v>4</v>
-      </c>
-      <c r="F16" s="5"/>
+      <c r="C16" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="53">
+        <v>1</v>
+      </c>
+      <c r="F16" s="58"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="50" t="s">
@@ -3640,10 +3644,10 @@
       </c>
       <c r="C17" s="51"/>
       <c r="D17" s="5" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E17" s="26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="5"/>
     </row>
@@ -3656,10 +3660,10 @@
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="5" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="E18" s="26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" s="5"/>
     </row>
@@ -3672,10 +3676,10 @@
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E19" s="26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="5"/>
     </row>
@@ -3688,7 +3692,7 @@
       </c>
       <c r="C20" s="51"/>
       <c r="D20" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E20" s="26">
         <v>4</v>
@@ -3704,10 +3708,10 @@
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21" s="26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="5"/>
     </row>
@@ -3720,10 +3724,10 @@
       </c>
       <c r="C22" s="51"/>
       <c r="D22" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E22" s="26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" s="5"/>
     </row>
@@ -3736,10 +3740,10 @@
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E23" s="26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F23" s="5"/>
     </row>
@@ -3752,10 +3756,10 @@
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E24" s="26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" s="5"/>
     </row>
@@ -3768,10 +3772,10 @@
       </c>
       <c r="C25" s="51"/>
       <c r="D25" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E25" s="26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F25" s="5"/>
     </row>
@@ -3784,10 +3788,10 @@
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E26" s="26">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F26" s="5"/>
     </row>
@@ -3798,12 +3802,12 @@
       <c r="B27" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="5"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E27" s="26">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F27" s="5"/>
     </row>
@@ -3816,12 +3820,28 @@
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="26">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E29" s="26">
         <v>5</v>
       </c>
-      <c r="F28" s="5"/>
+      <c r="F29" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
